--- a/manuscript_v5/SI/S11_Table.xlsx
+++ b/manuscript_v5/SI/S11_Table.xlsx
@@ -455,7 +455,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S11 Table. Patient-level label table, version 1.0 (A17): for each of the 489 platinum-treated patients, every candidate label, the strict combined label (recommended; 355 determinate) and the broad combined label (sensitivity analysis; 394), the re-derived platinum-free interval, and the provenance class, event source and flags of each re-derived call (A15, corrected run A15b); with a data dictionary, class counts, and the OS-threshold test characteristics against the broad and strict combined labels.</t>
+          <t>S11 Table. Patient-level label table, version 1.0 (A17): for each of the 489 platinum-treated patients, every candidate label, the provenance-filtered combined label (column label_combined_strict; recommended; 355 determinate) and the broad combined label (sensitivity analysis; 394), the re-derived platinum-free interval, and the provenance class, event source and flags of each re-derived call (A15, corrected run A15b); with a data dictionary, class counts, and the OS-threshold test characteristics against the broad and strict combined labels.</t>
         </is>
       </c>
     </row>
@@ -479,7 +479,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A15b (strict label as recommended): label_validity/outputs/a15b_provenance.csv, label_validity/outputs/a15b_class_by_group.csv, label_validity/outputs/a15b_resistant_event_source.csv, label_validity/outputs/a15b_os_test_strict.csv</t>
+          <t>A15b (provenance-filtered label as recommended): label_validity/outputs/a15b_provenance.csv, label_validity/outputs/a15b_class_by_group.csv, label_validity/outputs/a15b_resistant_event_source.csv, label_validity/outputs/a15b_os_test_strict.csv</t>
         </is>
       </c>
     </row>
@@ -33167,7 +33167,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RECOMMENDED label. 1 resistant, 0 sensitive, empty undetermined. TCGA 2011 platinum status where determinate; otherwise label_pfiplat6 only when provenance_class is clean_resistant or clean_sensitive (A15 header definition; script 15b).</t>
+          <t>RECOMMENDED label (the provenance-filtered combined label of the paper; a conservative extension of platinum status whose added calls are not verified). 1 resistant, 0 sensitive, empty undetermined. TCGA 2011 platinum status where determinate; otherwise label_pfiplat6 only when provenance_class is clean_resistant or clean_sensitive, i.e. unflagged (A15 header definition; script 15b).</t>
         </is>
       </c>
     </row>

--- a/manuscript_v5/SI/S11_Table.xlsx
+++ b/manuscript_v5/SI/S11_Table.xlsx
@@ -15,6 +15,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A15b_event_source" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A15b_os_test_strict" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A15_os_test_strict_asrun" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A20_discordant_patients" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A18_anchor_summary" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A18_anchor_counts" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -455,7 +458,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S11 Table. Patient-level label table, version 1.0 (A17): for each of the 489 platinum-treated patients, every candidate label, the provenance-filtered combined label (column label_combined_strict; recommended; 355 determinate) and the broad combined label (sensitivity analysis; 394), the re-derived platinum-free interval, and the provenance class, event source and flags of each re-derived call (A15, corrected run A15b); with a data dictionary, class counts, and the OS-threshold test characteristics against the broad and strict combined labels.</t>
+          <t>S11 Table. Patient-level label table, version 1.0 (A17): for each of the 489 platinum-treated patients, every candidate label, the provenance-filtered combined label (column label_combined_strict; a candidate extension, preferred under the pre-specified A15 rule; 355 determinate) and the broad combined label (sensitivity analysis; 394), the re-derived platinum-free interval, and the provenance class, event source and flags of each re-derived call (A15, corrected run A15b); with a data dictionary, class counts, and the OS-threshold test characteristics against the broad and strict combined labels.</t>
         </is>
       </c>
     </row>
@@ -493,6 +496,331 @@
         <is>
           <t>A15 (as first run, before the near-threshold flag was added): label_validity/outputs/a15_os_test_strict.csv; scorecard in S1 Text</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>anchor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>determinate</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>resistant</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>anchor_differs_from_A0</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>n_both_A0</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>changed_vs_A0</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>pct_changed</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>kappa_A0</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>n_both_platinum</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>agree_platinum</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>kappa_platinum</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A0</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>389</v>
+      </c>
+      <c r="C2" t="n">
+        <v>115</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>389</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>272</v>
+      </c>
+      <c r="J2" t="n">
+        <v>268</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.9662090813093982</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>389</v>
+      </c>
+      <c r="C3" t="n">
+        <v>110</v>
+      </c>
+      <c r="D3" t="n">
+        <v>55</v>
+      </c>
+      <c r="E3" t="n">
+        <v>389</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.2853470437018</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.9687424668541582</v>
+      </c>
+      <c r="I3" t="n">
+        <v>272</v>
+      </c>
+      <c r="J3" t="n">
+        <v>267</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.9573560767590618</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>407</v>
+      </c>
+      <c r="C4" t="n">
+        <v>121</v>
+      </c>
+      <c r="D4" t="n">
+        <v>56</v>
+      </c>
+      <c r="E4" t="n">
+        <v>389</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.2853470437018</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9687424668541582</v>
+      </c>
+      <c r="I4" t="n">
+        <v>276</v>
+      </c>
+      <c r="J4" t="n">
+        <v>270</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.9499546690843156</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>388</v>
+      </c>
+      <c r="C5" t="n">
+        <v>114</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>388</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>272</v>
+      </c>
+      <c r="J5" t="n">
+        <v>268</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.9662090813093982</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>patients with label_pfiplat6 determinate</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  with &gt;1 Adjuvant platinum row</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  with overlapping Adjuvant platinum rows</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  with &gt;1 Adjuvant platinum row sharing the max STOP_DATE</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  with an Adjuvant platinum row missing STOP_DATE</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  with an Adjuvant platinum row starting on/after the first Recurrence/Progression row</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  with any platinum row of indication Other or missing</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cohort patients without any Adjuvant platinum row</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -33167,7 +33495,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RECOMMENDED label (the provenance-filtered combined label of the paper; a conservative extension of platinum status whose added calls are not verified). 1 resistant, 0 sensitive, empty undetermined. TCGA 2011 platinum status where determinate; otherwise label_pfiplat6 only when provenance_class is clean_resistant or clean_sensitive, i.e. unflagged (A15 header definition; script 15b).</t>
+          <t>Provenance-filtered candidate extension of platinum status (preferred of the two combined labels under the pre-specified A15 rule; added calls not verified as accurate). 1 resistant, 0 sensitive, empty undetermined. TCGA 2011 platinum status where determinate; otherwise label_pfiplat6 only when provenance_class is clean_resistant or clean_sensitive, i.e. unflagged (A15 header definition; script 15b).</t>
         </is>
       </c>
     </row>
@@ -34563,4 +34891,315 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PATIENT_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>label_platinum</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>src_platinum_status_raw</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>label_pfiplat6</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>pfi_from_platinum_d</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>event_source</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>provenance_class</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>redacted</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>adj_platinum_rows</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>adj_platinum_stop_missing</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>later_line_before_event</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>near_threshold</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>label_A1</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>label_A2</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>label_A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TCGA-24-2029</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Sensitive</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>154</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>recorded_new_tumour_event:Recurrence</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>flagged</t>
+        </is>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TCGA-29-1774</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Sensitive</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>101</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>recorded_new_tumour_event:Recurrence</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>clean_resistant</t>
+        </is>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TCGA-61-2009</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Sensitive</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>recorded_new_tumour_event:Recurrence</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>clean_resistant</t>
+        </is>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TCGA-61-2113</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Sensitive</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>148</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>recorded_new_tumour_event:Recurrence</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>clean_resistant</t>
+        </is>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/manuscript_v5/SI/S11_Table.xlsx
+++ b/manuscript_v5/SI/S11_Table.xlsx
@@ -18,6 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A20_discordant_patients" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A18_anchor_summary" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A18_anchor_counts" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A21_event_type" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -435,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,6 +496,18 @@
       <c r="B5" t="inlineStr">
         <is>
           <t>A15 (as first run, before the near-threshold flag was added): label_validity/outputs/a15_os_test_strict.csv; scorecard in S1 Text</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>source / note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>A18 (anchor sensitivity), A20 (discordant patients), A21 (event-type sensitivity): label_validity/outputs/a18_anchor_summary.csv, label_validity/outputs/a18_anchor_counts.csv, label_validity/outputs/a20_discordant.csv, label_validity/outputs/a21_event_type.csv</t>
         </is>
       </c>
     </row>
@@ -828,6 +841,375 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>label_pfiplat6</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>label_pfiplat6_rec</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>determinate</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>389</v>
+      </c>
+      <c r="C2" t="n">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>resistant</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>115</v>
+      </c>
+      <c r="C3" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>n_with_platinum</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>272</v>
+      </c>
+      <c r="C4" t="n">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>kappa_platinum</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.9662090813093982</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9662090813093982</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>os18_n</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>375</v>
+      </c>
+      <c r="C6" t="n">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>os18_sens</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.2685185185185185</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.2346938775510204</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>os18_sens_lo</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.1939490138966897</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.1617847895187315</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>os18_sens_hi</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.3589895785785681</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.327617654219303</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>os18_ppv</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.7837837837837838</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.7419354838709677</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>os18_ppv_lo</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.6280485160803084</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.5675386419056621</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>os18_ppv_hi</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.8861348800661442</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.8629829409360625</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>os24_n</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>360</v>
+      </c>
+      <c r="C13" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>os24_sens</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.4392523364485981</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.4123711340206185</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>os24_sens_lo</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.3489409789836415</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.319573240177898</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>os24_sens_hi</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.5337743863831225</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5118453033575773</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>os24_ppv</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.734375</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7017543859649122</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>os24_ppv_lo</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.6151712627143486</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5733571989653998</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>os24_ppv_hi</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.8270362092577739</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.8046744992518191</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>brca_or</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.3700371789357881</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.3635983163575219</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>brca_lo</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.1406121602245019</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.1290659777457791</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>brca_hi</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.8670216984648549</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.8905123796948157</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>brca_n</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>226</v>
+      </c>
+      <c r="C23" t="n">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ccne1_or</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1.762615041028337</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.712691595414355</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ccne1_lo</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.976903968958708</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9271686778441116</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ccne1_hi</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>3.152332113385684</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3.123951545204223</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ccne1_n</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>340</v>
+      </c>
+      <c r="C27" t="n">
+        <v>331</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/manuscript_v5/SI/S11_Table.xlsx
+++ b/manuscript_v5/SI/S11_Table.xlsx
@@ -19,6 +19,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A18_anchor_summary" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A18_anchor_counts" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A21_event_type" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A23_anchor_checks" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1210,6 +1211,532 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>anchor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>became_undetermined</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>became_determinate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>all determinate</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>carbo_cis_only</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>389</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>all determinate</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>389</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>all determinate</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>389</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>all determinate</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>389</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>added (117)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>carbo_cis_only</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>117</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>added (117)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>117</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>added (117)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>117</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>added (117)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>117</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>unflagged added (78)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>carbo_cis_only</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>78</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>unflagged added (78)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>78</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>unflagged added (78)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>78</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>unflagged added (78)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>78</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>discordant (4)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>carbo_cis_only</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>discordant (4)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>discordant (4)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>discordant (4)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>unflagged added resistant with RNA-seq</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>carbo_cis_only</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>unflagged added resistant with RNA-seq</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>unflagged added resistant with RNA-seq</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>unflagged added resistant with RNA-seq</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -33961,7 +34488,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>clean_resistant (recorded new tumour event, no flag); clean_sensitive (interval &gt;= 183 days, no flag); flagged (any flag, or a resistant call from a death counted as progression); negative_interval.</t>
+          <t>'clean' means that no specified provenance flag applied, not that the call is clinically verified. clean_resistant (recorded new tumour event, of any recorded or unrecorded type, no flag; 2 of the 12 added clean_resistant calls have an unrecorded event type); clean_sensitive (interval &gt;= 183 days, no flag); flagged (any flag, or a resistant call from a death counted as progression); negative_interval.</t>
         </is>
       </c>
     </row>
